--- a/Config/Luban/source/TbMap.xlsx
+++ b/Config/Luban/source/TbMap.xlsx
@@ -337,16 +337,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -372,22 +370,7 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>width</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>length</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
           <t>cellSize</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>layoutVersion</t>
         </is>
       </c>
     </row>
@@ -417,21 +400,6 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
@@ -456,22 +424,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>场地宽度 X（米）</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>场地长度 Z（米）</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
           <t>归属网格边长（米）</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>场地布局协议版本</t>
         </is>
       </c>
     </row>
@@ -491,16 +444,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="G4" s="2" t="n">
         <v>0.125</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Luban/source/TbMap.xlsx
+++ b/Config/Luban/source/TbMap.xlsx
@@ -337,7 +337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -345,6 +345,10 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -373,6 +377,26 @@
           <t>cellSize</t>
         </is>
       </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>foamCellSize</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>foamChunkSize</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>foamMaxHeight</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>foamCeilingGap</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -400,6 +424,26 @@
           <t>float</t>
         </is>
       </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
@@ -425,6 +469,26 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>归属网格边长（米）</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>泡沫：高度采样间距（米）</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>泡沫：分块边长（米）</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>泡沫：最大新增高度（米）</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>泡沫：顶部障碍间隙（米）</t>
         </is>
       </c>
     </row>
@@ -446,6 +510,18 @@
       <c r="E4" s="2" t="n">
         <v>0.125</v>
       </c>
+      <c r="F4" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
